--- a/ESTIMATION.xlsx
+++ b/ESTIMATION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\programmer\OneDrive\Desktop\Use_cases\T Systems Everything\RFP Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE79FF8-F266-4DD9-BEFF-55FC21948D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75EAEAAD-E7F3-4E64-BD08-62DEE704527C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{85BCF0F2-A008-4200-B7F3-F3995E62932F}"/>
   </bookViews>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>Role</t>
   </si>
   <si>
-    <t>AI/ML Architect</t>
-  </si>
-  <si>
-    <t>LLM Engineer</t>
-  </si>
-  <si>
     <t>Data Engineer</t>
   </si>
   <si>
@@ -51,24 +45,6 @@
     <t>Business Analyst</t>
   </si>
   <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>Month 3 Mandays</t>
-  </si>
-  <si>
-    <t>Total Mandays</t>
-  </si>
-  <si>
-    <t>Month 2 Mandays</t>
-  </si>
-  <si>
-    <t>Month 1 Mandays</t>
-  </si>
-  <si>
-    <t>Responsibility</t>
-  </si>
-  <si>
     <t>Allocation</t>
   </si>
   <si>
@@ -78,21 +54,12 @@
     <t>20–30%</t>
   </si>
   <si>
-    <t>LangChain, prompt design, validation logic</t>
-  </si>
-  <si>
-    <t>Data pipelines, Service Bus, Blob, processing</t>
-  </si>
-  <si>
     <t>FastAPI, APIs, integration with claims system</t>
   </si>
   <si>
     <t>Deployment, monitoring, CI/CD, scaling</t>
   </si>
   <si>
-    <t>QA/Test Engineer</t>
-  </si>
-  <si>
     <t>Functional + integration testing</t>
   </si>
   <si>
@@ -102,14 +69,83 @@
     <t>30–40%</t>
   </si>
   <si>
-    <t>Delivery tracking, coordination</t>
+    <t>Month 1</t>
+  </si>
+  <si>
+    <t>Month 2</t>
+  </si>
+  <si>
+    <t>Month 3</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Lead AI/ML Architect</t>
+  </si>
+  <si>
+    <t>Machine Learning Engineer</t>
+  </si>
+  <si>
+    <t>Data Scientist</t>
+  </si>
+  <si>
+    <t>Integration Engineer</t>
+  </si>
+  <si>
+    <t>AI Platform Engineer</t>
+  </si>
+  <si>
+    <t>Security Engineer</t>
+  </si>
+  <si>
+    <t>Product Owner</t>
+  </si>
+  <si>
+    <t>RFP Role</t>
+  </si>
+  <si>
+    <t>Responsibility in MVP1</t>
+  </si>
+  <si>
+    <t>LangChain-based agent design, prompt engineering, validation logic (LLM work included)</t>
+  </si>
+  <si>
+    <t>Validation rules, confidence scoring, business logic tuning</t>
+  </si>
+  <si>
+    <t>50–70%</t>
+  </si>
+  <si>
+    <t>Data pipelines, Azure Service Bus, Blob, processing</t>
+  </si>
+  <si>
+    <t>Backend / Software Engineer</t>
+  </si>
+  <si>
+    <t>External system integration, claims API connectivity</t>
+  </si>
+  <si>
+    <t>Azure setup, OpenAI integration, infra configuration</t>
+  </si>
+  <si>
+    <t>QA / Test Engineer</t>
+  </si>
+  <si>
+    <t>AI Product Owner / PM</t>
+  </si>
+  <si>
+    <t>Delivery tracking, prioritization, coordination</t>
+  </si>
+  <si>
+    <t>Security controls, compliance, audit readiness</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,40 +169,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -174,56 +186,129 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -234,6 +319,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{89023D80-EC4C-4E8F-BA26-3750CDA4ED6C}" name="Table1" displayName="Table1" ref="L42:N54" totalsRowShown="0" headerRowDxfId="7">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{D14080B6-4727-4D35-BD81-DDEFF9EEFC72}" name="RFP Role" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{349908A4-EFE1-4F1B-BE58-2B4317F383DE}" name="Responsibility in MVP1" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{591E17AC-964B-402E-B2BE-90EFD7A19D72}" name="Allocation" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9F36478-2695-45D7-9D75-AE688C52E080}" name="Table2" displayName="Table2" ref="E17:I29" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{8AB3DD1F-CF1A-43B5-ABB0-9AA266E27AF7}" name="Role" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{6625C17C-B620-4718-BB8E-62BC9497CCF0}" name="Month 1" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{4A5ABC1E-CAC0-43F7-A569-BEB904BA0945}" name="Month 2" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{A145A45D-EC07-4232-8CE9-B2131C8D8793}" name="Month 3" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{05B93EAF-801A-4467-82E1-A171BF2CA88C}" name="Total" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -533,272 +642,432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A433EC1-D0DD-4099-B4A6-A36D6DD87C68}">
-  <dimension ref="E17:N38"/>
+  <dimension ref="E17:N54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="6" max="7" width="10.5703125" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="17" spans="5:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="E17" s="1" t="s">
+    <row r="17" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E17" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="6">
+        <v>8</v>
+      </c>
+      <c r="G18" s="6">
+        <v>6</v>
+      </c>
+      <c r="H18" s="6">
+        <v>4</v>
+      </c>
+      <c r="I18" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="6">
+        <v>20</v>
+      </c>
+      <c r="G19" s="6">
+        <v>20</v>
+      </c>
+      <c r="H19" s="6">
+        <v>20</v>
+      </c>
+      <c r="I19" s="6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="6">
+        <v>10</v>
+      </c>
+      <c r="G20" s="6">
+        <v>15</v>
+      </c>
+      <c r="H20" s="6">
+        <v>10</v>
+      </c>
+      <c r="I20" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E21" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6">
+        <v>20</v>
+      </c>
+      <c r="G21" s="6">
+        <v>20</v>
+      </c>
+      <c r="H21" s="6">
+        <v>15</v>
+      </c>
+      <c r="I21" s="6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6">
+        <v>20</v>
+      </c>
+      <c r="G22" s="6">
+        <v>20</v>
+      </c>
+      <c r="H22" s="6">
+        <v>15</v>
+      </c>
+      <c r="I22" s="6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="6">
+        <v>10</v>
+      </c>
+      <c r="G23" s="6">
+        <v>15</v>
+      </c>
+      <c r="H23" s="6">
+        <v>15</v>
+      </c>
+      <c r="I23" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="6">
+        <v>10</v>
+      </c>
+      <c r="G24" s="6">
+        <v>10</v>
+      </c>
+      <c r="H24" s="6">
+        <v>10</v>
+      </c>
+      <c r="I24" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E25" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="6">
+        <v>5</v>
+      </c>
+      <c r="G25" s="6">
+        <v>10</v>
+      </c>
+      <c r="H25" s="6">
+        <v>15</v>
+      </c>
+      <c r="I25" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="6">
+        <v>5</v>
+      </c>
+      <c r="G26" s="6">
+        <v>5</v>
+      </c>
+      <c r="H26" s="6">
+        <v>5</v>
+      </c>
+      <c r="I26" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="6">
+        <v>5</v>
+      </c>
+      <c r="G27" s="6">
+        <v>10</v>
+      </c>
+      <c r="H27" s="6">
+        <v>15</v>
+      </c>
+      <c r="I27" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="6">
+        <v>10</v>
+      </c>
+      <c r="G28" s="6">
+        <v>5</v>
+      </c>
+      <c r="H28" s="6">
+        <v>5</v>
+      </c>
+      <c r="I28" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="6">
+        <v>5</v>
+      </c>
+      <c r="G29" s="6">
+        <v>5</v>
+      </c>
+      <c r="H29" s="6">
+        <v>5</v>
+      </c>
+      <c r="I29" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+    </row>
+    <row r="31" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="L31" s="8"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+    </row>
+    <row r="32" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="L32" s="8"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L33" s="8"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L34" s="8"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L35" s="8"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="10"/>
+    </row>
+    <row r="36" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L36" s="8"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="10"/>
+    </row>
+    <row r="37" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L37" s="8"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+    </row>
+    <row r="38" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L38" s="8"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+    </row>
+    <row r="42" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="L43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="12:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="L44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N44" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="L45" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="L46" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="12:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="L47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N47" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="L48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="L49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="L51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4">
-        <v>8</v>
-      </c>
-      <c r="G18" s="4">
-        <v>6</v>
-      </c>
-      <c r="H18" s="4">
-        <v>4</v>
-      </c>
-      <c r="I18" s="4">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E19" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F19" s="4">
-        <v>20</v>
-      </c>
-      <c r="G19" s="4">
-        <v>20</v>
-      </c>
-      <c r="H19" s="4">
-        <v>20</v>
-      </c>
-      <c r="I19" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="4">
-        <v>20</v>
-      </c>
-      <c r="G20" s="4">
-        <v>20</v>
-      </c>
-      <c r="H20" s="4">
-        <v>15</v>
-      </c>
-      <c r="I20" s="4">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="4">
-        <v>20</v>
-      </c>
-      <c r="G21" s="4">
-        <v>20</v>
-      </c>
-      <c r="H21" s="4">
-        <v>15</v>
-      </c>
-      <c r="I21" s="4">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="4">
-        <v>5</v>
-      </c>
-      <c r="G22" s="4">
-        <v>10</v>
-      </c>
-      <c r="H22" s="4">
-        <v>15</v>
-      </c>
-      <c r="I22" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="4">
-        <v>5</v>
-      </c>
-      <c r="G23" s="4">
-        <v>10</v>
-      </c>
-      <c r="H23" s="4">
-        <v>15</v>
-      </c>
-      <c r="I23" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="4">
-        <v>10</v>
-      </c>
-      <c r="G24" s="4">
-        <v>5</v>
-      </c>
-      <c r="H24" s="4">
-        <v>5</v>
-      </c>
-      <c r="I24" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="4">
-        <v>8</v>
-      </c>
-      <c r="G25" s="4">
-        <v>8</v>
-      </c>
-      <c r="H25" s="4">
-        <v>8</v>
-      </c>
-      <c r="I25" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="L30" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="s">
+      <c r="N52" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N30" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="L31" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="L32" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N32" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L33" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L34" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N34" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L35" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="N35" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N36" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="37" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L37" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M37" s="7" t="s">
+    </row>
+    <row r="53" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="L53" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="12:14" x14ac:dyDescent="0.25">
+      <c r="L54" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="N37" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L38" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N38" s="7" t="s">
-        <v>24</v>
+      <c r="M54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/ESTIMATION.xlsx
+++ b/ESTIMATION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\programmer\OneDrive\Desktop\Use_cases\T Systems Everything\RFP Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75EAEAAD-E7F3-4E64-BD08-62DEE704527C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87138CE2-C5E2-4FF5-BF27-89372B9642DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{85BCF0F2-A008-4200-B7F3-F3995E62932F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>Role</t>
   </si>
@@ -139,6 +139,90 @@
   </si>
   <si>
     <t>Security controls, compliance, audit readiness</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Key Activities</t>
+  </si>
+  <si>
+    <t>Primary Roles</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <r>
+      <t>Month 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Foundation &amp; Setup</t>
+    </r>
+  </si>
+  <si>
+    <t>Architecture finalization, Azure setup (Blob, Service Bus, OpenAI), FastAPI ingestion, email integration, validation, security baseline</t>
+  </si>
+  <si>
+    <t>AI/ML Architect, Backend Engineer, Data Engineer, AI Platform Engineer, Business Analyst, Security Engineer</t>
+  </si>
+  <si>
+    <t>Working ingestion pipeline + infra ready</t>
+  </si>
+  <si>
+    <r>
+      <t>Month 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI &amp; Processing</t>
+    </r>
+  </si>
+  <si>
+    <t>LangChain pipeline, LLM integration, classification–extraction–validation flow, OCR processing, rule engine, initial backend integration</t>
+  </si>
+  <si>
+    <t>ML Engineer, Data Scientist, Data Engineer, Backend Engineer, Integration Engineer</t>
+  </si>
+  <si>
+    <t>End-to-end AI processing pipeline</t>
+  </si>
+  <si>
+    <r>
+      <t>Month 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integration &amp; Deployment</t>
+    </r>
+  </si>
+  <si>
+    <t>End-to-end testing, human-in-loop workflow, performance tuning, monitoring setup, CI/CD, deployment</t>
+  </si>
+  <si>
+    <t>QA Engineer, MLOps Engineer, Integration Engineer, Backend Engineer, Product Owner, Security Engineer</t>
+  </si>
+  <si>
+    <t>Production-ready MVP deployment</t>
   </si>
 </sst>
 </file>
@@ -190,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,23 +294,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="17">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -250,19 +408,29 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -283,31 +451,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -322,24 +465,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{89023D80-EC4C-4E8F-BA26-3750CDA4ED6C}" name="Table1" displayName="Table1" ref="L42:N54" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{89023D80-EC4C-4E8F-BA26-3750CDA4ED6C}" name="Table1" displayName="Table1" ref="L42:N54" totalsRowShown="0" headerRowDxfId="16">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D14080B6-4727-4D35-BD81-DDEFF9EEFC72}" name="RFP Role" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{349908A4-EFE1-4F1B-BE58-2B4317F383DE}" name="Responsibility in MVP1" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{591E17AC-964B-402E-B2BE-90EFD7A19D72}" name="Allocation" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{D14080B6-4727-4D35-BD81-DDEFF9EEFC72}" name="RFP Role" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{349908A4-EFE1-4F1B-BE58-2B4317F383DE}" name="Responsibility in MVP1" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{591E17AC-964B-402E-B2BE-90EFD7A19D72}" name="Allocation" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9F36478-2695-45D7-9D75-AE688C52E080}" name="Table2" displayName="Table2" ref="E17:I29" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9F36478-2695-45D7-9D75-AE688C52E080}" name="Table2" displayName="Table2" ref="E17:I29" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8AB3DD1F-CF1A-43B5-ABB0-9AA266E27AF7}" name="Role" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{6625C17C-B620-4718-BB8E-62BC9497CCF0}" name="Month 1" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{4A5ABC1E-CAC0-43F7-A569-BEB904BA0945}" name="Month 2" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{A145A45D-EC07-4232-8CE9-B2131C8D8793}" name="Month 3" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{05B93EAF-801A-4467-82E1-A171BF2CA88C}" name="Total" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{8AB3DD1F-CF1A-43B5-ABB0-9AA266E27AF7}" name="Role" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{6625C17C-B620-4718-BB8E-62BC9497CCF0}" name="Month 1" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{4A5ABC1E-CAC0-43F7-A569-BEB904BA0945}" name="Month 2" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{A145A45D-EC07-4232-8CE9-B2131C8D8793}" name="Month 3" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{05B93EAF-801A-4467-82E1-A171BF2CA88C}" name="Total" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5115CA64-B1BE-420B-81BF-0113ECC1EB93}" name="Table3" displayName="Table3" ref="P56:S59" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{383A7F68-723D-4D6B-B681-834832A6B569}" name="Phase" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{953A1284-F656-4699-BEB5-CED10A77D631}" name="Key Activities" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{4BCC30B5-A8D6-4378-8155-67AC06CC9BAD}" name="Primary Roles" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{F4B9DDE3-5EA7-4983-AFD6-B211F4B5EDF6}" name="Output" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -642,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A433EC1-D0DD-4099-B4A6-A36D6DD87C68}">
-  <dimension ref="E17:N54"/>
+  <dimension ref="E17:S59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -652,6 +807,10 @@
     <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="44.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="30.85546875" customWidth="1"/>
+    <col min="17" max="17" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="17" spans="5:14" x14ac:dyDescent="0.25">
@@ -997,7 +1156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L49" s="4" t="s">
         <v>22</v>
       </c>
@@ -1008,7 +1167,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="12:19" x14ac:dyDescent="0.25">
       <c r="L50" s="4" t="s">
         <v>3</v>
       </c>
@@ -1019,7 +1178,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L51" s="4" t="s">
         <v>34</v>
       </c>
@@ -1030,7 +1189,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="12:19" x14ac:dyDescent="0.25">
       <c r="L52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1041,7 +1200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="12:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L53" s="4" t="s">
         <v>35</v>
       </c>
@@ -1052,7 +1211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="12:19" x14ac:dyDescent="0.25">
       <c r="L54" s="4" t="s">
         <v>23</v>
       </c>
@@ -1063,11 +1222,68 @@
         <v>13</v>
       </c>
     </row>
+    <row r="56" spans="12:19" x14ac:dyDescent="0.25">
+      <c r="P56" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q56" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="R56" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S56" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="12:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="P57" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q57" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="R57" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="S57" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="12:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="P58" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="R58" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="S58" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="12:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="P59" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q59" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="R59" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="S59" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/ESTIMATION.xlsx
+++ b/ESTIMATION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\programmer\OneDrive\Desktop\Use_cases\T Systems Everything\RFP Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87138CE2-C5E2-4FF5-BF27-89372B9642DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAFBE88-0341-4E06-9225-51A605DEEC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{85BCF0F2-A008-4200-B7F3-F3995E62932F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
     <t>Role</t>
   </si>
@@ -48,24 +48,9 @@
     <t>Allocation</t>
   </si>
   <si>
-    <t>Overall solution design, AI strategy, governance</t>
-  </si>
-  <si>
     <t>20–30%</t>
   </si>
   <si>
-    <t>FastAPI, APIs, integration with claims system</t>
-  </si>
-  <si>
-    <t>Deployment, monitoring, CI/CD, scaling</t>
-  </si>
-  <si>
-    <t>Functional + integration testing</t>
-  </si>
-  <si>
-    <t>Requirements, validation rules, use cases</t>
-  </si>
-  <si>
     <t>30–40%</t>
   </si>
   <si>
@@ -105,27 +90,12 @@
     <t>RFP Role</t>
   </si>
   <si>
-    <t>Responsibility in MVP1</t>
-  </si>
-  <si>
-    <t>LangChain-based agent design, prompt engineering, validation logic (LLM work included)</t>
-  </si>
-  <si>
-    <t>Validation rules, confidence scoring, business logic tuning</t>
-  </si>
-  <si>
     <t>50–70%</t>
   </si>
   <si>
-    <t>Data pipelines, Azure Service Bus, Blob, processing</t>
-  </si>
-  <si>
     <t>Backend / Software Engineer</t>
   </si>
   <si>
-    <t>External system integration, claims API connectivity</t>
-  </si>
-  <si>
     <t>Azure setup, OpenAI integration, infra configuration</t>
   </si>
   <si>
@@ -135,12 +105,6 @@
     <t>AI Product Owner / PM</t>
   </si>
   <si>
-    <t>Delivery tracking, prioritization, coordination</t>
-  </si>
-  <si>
-    <t>Security controls, compliance, audit readiness</t>
-  </si>
-  <si>
     <t>Phase</t>
   </si>
   <si>
@@ -153,8 +117,50 @@
     <t>Output</t>
   </si>
   <si>
+    <t>Responsibility in MVP2</t>
+  </si>
+  <si>
+    <t>Overall architecture, AI strategy, governance, solution design</t>
+  </si>
+  <si>
+    <t>Agent design, LLM orchestration, prompt engineering, tool-calling logic</t>
+  </si>
+  <si>
+    <t>Risk logic, scoring models, validation rules, business tuning</t>
+  </si>
+  <si>
+    <t>Data pipelines, integration with internal systems, data transformation</t>
+  </si>
+  <si>
+    <t>FastAPI services, orchestration, API development</t>
+  </si>
+  <si>
+    <t>MCP/tool connectors, external system integrations, APIs</t>
+  </si>
+  <si>
+    <t>70–100%</t>
+  </si>
+  <si>
+    <t>Deployment, CI/CD, monitoring, scaling</t>
+  </si>
+  <si>
+    <t>Functional testing, integration testing, validation</t>
+  </si>
+  <si>
+    <t>Requirements, underwriting rules, use case definition</t>
+  </si>
+  <si>
+    <t>Planning, prioritization, delivery tracking</t>
+  </si>
+  <si>
+    <t>RBAC, compliance, API security, audit readiness</t>
+  </si>
+  <si>
+    <t>Underwriter dashboard design, user flows, usability</t>
+  </si>
+  <si>
     <r>
-      <t>Month 1</t>
+      <t>UI/UX Designer</t>
     </r>
     <r>
       <rPr>
@@ -164,65 +170,44 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Foundation &amp; Setup</t>
+      <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
-    <t>Architecture finalization, Azure setup (Blob, Service Bus, OpenAI), FastAPI ingestion, email integration, validation, security baseline</t>
-  </si>
-  <si>
-    <t>AI/ML Architect, Backend Engineer, Data Engineer, AI Platform Engineer, Business Analyst, Security Engineer</t>
-  </si>
-  <si>
-    <t>Working ingestion pipeline + infra ready</t>
-  </si>
-  <si>
-    <r>
-      <t>Month 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AI &amp; Processing</t>
-    </r>
-  </si>
-  <si>
-    <t>LangChain pipeline, LLM integration, classification–extraction–validation flow, OCR processing, rule engine, initial backend integration</t>
-  </si>
-  <si>
-    <t>ML Engineer, Data Scientist, Data Engineer, Backend Engineer, Integration Engineer</t>
-  </si>
-  <si>
-    <t>End-to-end AI processing pipeline</t>
-  </si>
-  <si>
-    <r>
-      <t>Month 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Integration &amp; Deployment</t>
-    </r>
-  </si>
-  <si>
-    <t>End-to-end testing, human-in-loop workflow, performance tuning, monitoring setup, CI/CD, deployment</t>
-  </si>
-  <si>
-    <t>QA Engineer, MLOps Engineer, Integration Engineer, Backend Engineer, Product Owner, Security Engineer</t>
-  </si>
-  <si>
-    <t>Production-ready MVP deployment</t>
+    <t>Month 1: Foundation &amp; Setup</t>
+  </si>
+  <si>
+    <t>Architecture finalization, Azure setup, FastAPI backend setup, Claims API integration, initial UI/UX design, security baseline</t>
+  </si>
+  <si>
+    <t>AI/ML Architect, Backend Engineer, Data Engineer, AI Platform Engineer, Business Analyst, UI/UX Designer, Security Engineer</t>
+  </si>
+  <si>
+    <t>Core backend, infra, and UI foundation ready</t>
+  </si>
+  <si>
+    <t>Month 2: AI &amp; Integration</t>
+  </si>
+  <si>
+    <t>LLM integration, agent workflow setup, tool (MCP) connectors to internal &amp; external systems, risk logic implementation, dashboard development</t>
+  </si>
+  <si>
+    <t>ML Engineer, Data Scientist, Backend Engineer, Integration Engineer, Data Engineer, UI/UX Designer</t>
+  </si>
+  <si>
+    <t>End-to-end AI + data integration pipeline</t>
+  </si>
+  <si>
+    <t>Month 3: Testing &amp; Deployment</t>
+  </si>
+  <si>
+    <t>End-to-end testing, human-in-the-loop workflow, UI refinement, performance tuning, monitoring setup, CI/CD, deployment</t>
+  </si>
+  <si>
+    <t>QA Engineer, MLOps Engineer, Backend Engineer, Integration Engineer, Product Owner, Security Engineer</t>
+  </si>
+  <si>
+    <t>Production-ready MVP with UI and decision workflow</t>
   </si>
 </sst>
 </file>
@@ -274,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -288,12 +273,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -306,152 +285,11 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -465,36 +303,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{89023D80-EC4C-4E8F-BA26-3750CDA4ED6C}" name="Table1" displayName="Table1" ref="L42:N54" totalsRowShown="0" headerRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{89023D80-EC4C-4E8F-BA26-3750CDA4ED6C}" name="Table1" displayName="Table1" ref="L42:N55" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D14080B6-4727-4D35-BD81-DDEFF9EEFC72}" name="RFP Role" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{349908A4-EFE1-4F1B-BE58-2B4317F383DE}" name="Responsibility in MVP1" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{591E17AC-964B-402E-B2BE-90EFD7A19D72}" name="Allocation" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{D14080B6-4727-4D35-BD81-DDEFF9EEFC72}" name="RFP Role"/>
+    <tableColumn id="2" xr3:uid="{349908A4-EFE1-4F1B-BE58-2B4317F383DE}" name="Responsibility in MVP2"/>
+    <tableColumn id="3" xr3:uid="{591E17AC-964B-402E-B2BE-90EFD7A19D72}" name="Allocation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9F36478-2695-45D7-9D75-AE688C52E080}" name="Table2" displayName="Table2" ref="E17:I29" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9F36478-2695-45D7-9D75-AE688C52E080}" name="Table2" displayName="Table2" ref="E17:I30" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8AB3DD1F-CF1A-43B5-ABB0-9AA266E27AF7}" name="Role" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{6625C17C-B620-4718-BB8E-62BC9497CCF0}" name="Month 1" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{4A5ABC1E-CAC0-43F7-A569-BEB904BA0945}" name="Month 2" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{A145A45D-EC07-4232-8CE9-B2131C8D8793}" name="Month 3" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{05B93EAF-801A-4467-82E1-A171BF2CA88C}" name="Total" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{8AB3DD1F-CF1A-43B5-ABB0-9AA266E27AF7}" name="Role"/>
+    <tableColumn id="2" xr3:uid="{6625C17C-B620-4718-BB8E-62BC9497CCF0}" name="Month 1"/>
+    <tableColumn id="3" xr3:uid="{4A5ABC1E-CAC0-43F7-A569-BEB904BA0945}" name="Month 2"/>
+    <tableColumn id="4" xr3:uid="{A145A45D-EC07-4232-8CE9-B2131C8D8793}" name="Month 3"/>
+    <tableColumn id="5" xr3:uid="{05B93EAF-801A-4467-82E1-A171BF2CA88C}" name="Total"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5115CA64-B1BE-420B-81BF-0113ECC1EB93}" name="Table3" displayName="Table3" ref="P56:S59" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5115CA64-B1BE-420B-81BF-0113ECC1EB93}" name="Table3" displayName="Table3" ref="P56:S59" totalsRowShown="0">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{383A7F68-723D-4D6B-B681-834832A6B569}" name="Phase" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{953A1284-F656-4699-BEB5-CED10A77D631}" name="Key Activities" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{4BCC30B5-A8D6-4378-8155-67AC06CC9BAD}" name="Primary Roles" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{F4B9DDE3-5EA7-4983-AFD6-B211F4B5EDF6}" name="Output" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{383A7F68-723D-4D6B-B681-834832A6B569}" name="Phase"/>
+    <tableColumn id="2" xr3:uid="{953A1284-F656-4699-BEB5-CED10A77D631}" name="Key Activities"/>
+    <tableColumn id="3" xr3:uid="{4BCC30B5-A8D6-4378-8155-67AC06CC9BAD}" name="Primary Roles"/>
+    <tableColumn id="4" xr3:uid="{F4B9DDE3-5EA7-4983-AFD6-B211F4B5EDF6}" name="Output"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -814,277 +652,292 @@
   </cols>
   <sheetData>
     <row r="17" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2">
+        <v>4</v>
+      </c>
+      <c r="I18" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="F19" s="2">
+        <v>20</v>
+      </c>
+      <c r="G19" s="2">
+        <v>20</v>
+      </c>
+      <c r="H19" s="2">
+        <v>20</v>
+      </c>
+      <c r="I19" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="F20" s="2">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2">
+        <v>10</v>
+      </c>
+      <c r="I20" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>20</v>
+      </c>
+      <c r="G21" s="2">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2">
+        <v>15</v>
+      </c>
+      <c r="I21" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E22" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>20</v>
+      </c>
+      <c r="G22" s="2">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2">
+        <v>15</v>
+      </c>
+      <c r="I23" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="5:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="E24" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="5:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="E18" s="6" t="s">
+      <c r="F24" s="2">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2">
+        <v>10</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2">
+        <v>10</v>
+      </c>
+      <c r="H25" s="2">
+        <v>15</v>
+      </c>
+      <c r="I25" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="6">
-        <v>8</v>
-      </c>
-      <c r="G18" s="6">
-        <v>6</v>
-      </c>
-      <c r="H18" s="6">
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>5</v>
+      </c>
+      <c r="H26" s="2">
+        <v>5</v>
+      </c>
+      <c r="I26" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="6">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="5:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="E19" s="6" t="s">
+      <c r="F27" s="2">
+        <v>5</v>
+      </c>
+      <c r="G27" s="2">
+        <v>10</v>
+      </c>
+      <c r="H27" s="2">
+        <v>15</v>
+      </c>
+      <c r="I27" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
+        <v>5</v>
+      </c>
+      <c r="H28" s="2">
+        <v>5</v>
+      </c>
+      <c r="I28" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F29" s="2">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2">
+        <v>5</v>
+      </c>
+      <c r="H29" s="2">
+        <v>5</v>
+      </c>
+      <c r="I29" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="4">
+        <v>10</v>
+      </c>
+      <c r="G30" s="4">
+        <v>5</v>
+      </c>
+      <c r="H30" s="4">
+        <v>5</v>
+      </c>
+      <c r="I30" s="4">
         <v>20</v>
       </c>
-      <c r="G19" s="6">
-        <v>20</v>
-      </c>
-      <c r="H19" s="6">
-        <v>20</v>
-      </c>
-      <c r="I19" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E20" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="6">
-        <v>10</v>
-      </c>
-      <c r="G20" s="6">
-        <v>15</v>
-      </c>
-      <c r="H20" s="6">
-        <v>10</v>
-      </c>
-      <c r="I20" s="6">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E21" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="6">
-        <v>20</v>
-      </c>
-      <c r="G21" s="6">
-        <v>20</v>
-      </c>
-      <c r="H21" s="6">
-        <v>15</v>
-      </c>
-      <c r="I21" s="6">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E22" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" s="6">
-        <v>20</v>
-      </c>
-      <c r="G22" s="6">
-        <v>20</v>
-      </c>
-      <c r="H22" s="6">
-        <v>15</v>
-      </c>
-      <c r="I22" s="6">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="5:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="E23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="6">
-        <v>10</v>
-      </c>
-      <c r="G23" s="6">
-        <v>15</v>
-      </c>
-      <c r="H23" s="6">
-        <v>15</v>
-      </c>
-      <c r="I23" s="6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="5:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="E24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="6">
-        <v>10</v>
-      </c>
-      <c r="G24" s="6">
-        <v>10</v>
-      </c>
-      <c r="H24" s="6">
-        <v>10</v>
-      </c>
-      <c r="I24" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E25" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25" s="6">
-        <v>5</v>
-      </c>
-      <c r="G25" s="6">
-        <v>10</v>
-      </c>
-      <c r="H25" s="6">
-        <v>15</v>
-      </c>
-      <c r="I25" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="6">
-        <v>5</v>
-      </c>
-      <c r="G26" s="6">
-        <v>5</v>
-      </c>
-      <c r="H26" s="6">
-        <v>5</v>
-      </c>
-      <c r="I26" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E27" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="6">
-        <v>5</v>
-      </c>
-      <c r="G27" s="6">
-        <v>10</v>
-      </c>
-      <c r="H27" s="6">
-        <v>15</v>
-      </c>
-      <c r="I27" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E28" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="6">
-        <v>10</v>
-      </c>
-      <c r="G28" s="6">
-        <v>5</v>
-      </c>
-      <c r="H28" s="6">
-        <v>5</v>
-      </c>
-      <c r="I28" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="6">
-        <v>5</v>
-      </c>
-      <c r="G29" s="6">
-        <v>5</v>
-      </c>
-      <c r="H29" s="6">
-        <v>5</v>
-      </c>
-      <c r="I29" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
     </row>
     <row r="31" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="L31" s="8"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
     </row>
     <row r="32" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="L32" s="8"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="10"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="8"/>
     </row>
     <row r="33" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L33" s="8"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="10"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="8"/>
     </row>
     <row r="34" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L34" s="8"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="10"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="8"/>
     </row>
     <row r="35" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L35" s="8"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="10"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="8"/>
     </row>
     <row r="36" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L36" s="8"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="10"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="8"/>
     </row>
     <row r="37" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L37" s="8"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
     </row>
     <row r="38" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L38" s="8"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
     </row>
     <row r="42" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L42" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>6</v>
@@ -1092,21 +945,21 @@
     </row>
     <row r="43" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L43" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N43" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="12:14" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L44" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N44" s="3">
         <v>1</v>
@@ -1114,13 +967,13 @@
     </row>
     <row r="45" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L45" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="12:14" ht="30" x14ac:dyDescent="0.25">
@@ -1128,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N46" s="3">
         <v>1</v>
@@ -1136,10 +989,10 @@
     </row>
     <row r="47" spans="12:14" ht="45" x14ac:dyDescent="0.25">
       <c r="L47" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -1147,24 +1000,24 @@
     </row>
     <row r="48" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L48" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L49" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="12:19" x14ac:dyDescent="0.25">
@@ -1172,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="N50" s="3">
         <v>0.5</v>
@@ -1180,102 +1033,113 @@
     </row>
     <row r="51" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L51" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N51" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="12:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L52" s="4" t="s">
         <v>5</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L53" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="12:19" x14ac:dyDescent="0.25">
       <c r="L54" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="12:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="L55" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="12:19" x14ac:dyDescent="0.25">
-      <c r="P56" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q56" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="R56" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="S56" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="12:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="P57" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q57" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="R57" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="S57" s="13" t="s">
+      <c r="P56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="12:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="P57" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="Q57" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="58" spans="12:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="P58" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q58" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="R58" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="S58" s="13" t="s">
+      <c r="P58" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="Q58" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="59" spans="12:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="P59" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q59" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="R59" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="S59" s="13" t="s">
+      <c r="P59" s="4" t="s">
         <v>53</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/ESTIMATION.xlsx
+++ b/ESTIMATION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\programmer\OneDrive\Desktop\Use_cases\T Systems Everything\RFP Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAFBE88-0341-4E06-9225-51A605DEEC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61EAC8E-0582-4317-8C08-7218B3CBFBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{85BCF0F2-A008-4200-B7F3-F3995E62932F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
   <si>
     <t>Role</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Allocation</t>
   </si>
   <si>
-    <t>20–30%</t>
-  </si>
-  <si>
     <t>30–40%</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>Backend / Software Engineer</t>
   </si>
   <si>
-    <t>Azure setup, OpenAI integration, infra configuration</t>
-  </si>
-  <si>
     <t>QA / Test Engineer</t>
   </si>
   <si>
@@ -111,103 +105,106 @@
     <t>Key Activities</t>
   </si>
   <si>
-    <t>Primary Roles</t>
-  </si>
-  <si>
     <t>Output</t>
   </si>
   <si>
-    <t>Responsibility in MVP2</t>
-  </si>
-  <si>
-    <t>Overall architecture, AI strategy, governance, solution design</t>
-  </si>
-  <si>
-    <t>Agent design, LLM orchestration, prompt engineering, tool-calling logic</t>
-  </si>
-  <si>
-    <t>Risk logic, scoring models, validation rules, business tuning</t>
-  </si>
-  <si>
-    <t>Data pipelines, integration with internal systems, data transformation</t>
-  </si>
-  <si>
-    <t>FastAPI services, orchestration, API development</t>
-  </si>
-  <si>
-    <t>MCP/tool connectors, external system integrations, APIs</t>
-  </si>
-  <si>
     <t>70–100%</t>
   </si>
   <si>
-    <t>Deployment, CI/CD, monitoring, scaling</t>
-  </si>
-  <si>
-    <t>Functional testing, integration testing, validation</t>
-  </si>
-  <si>
-    <t>Requirements, underwriting rules, use case definition</t>
-  </si>
-  <si>
-    <t>Planning, prioritization, delivery tracking</t>
-  </si>
-  <si>
-    <t>RBAC, compliance, API security, audit readiness</t>
-  </si>
-  <si>
-    <t>Underwriter dashboard design, user flows, usability</t>
-  </si>
-  <si>
-    <r>
-      <t>UI/UX Designer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>Month 1: Foundation &amp; Setup</t>
-  </si>
-  <si>
-    <t>Architecture finalization, Azure setup, FastAPI backend setup, Claims API integration, initial UI/UX design, security baseline</t>
-  </si>
-  <si>
-    <t>AI/ML Architect, Backend Engineer, Data Engineer, AI Platform Engineer, Business Analyst, UI/UX Designer, Security Engineer</t>
-  </si>
-  <si>
-    <t>Core backend, infra, and UI foundation ready</t>
-  </si>
-  <si>
-    <t>Month 2: AI &amp; Integration</t>
-  </si>
-  <si>
-    <t>LLM integration, agent workflow setup, tool (MCP) connectors to internal &amp; external systems, risk logic implementation, dashboard development</t>
-  </si>
-  <si>
-    <t>ML Engineer, Data Scientist, Backend Engineer, Integration Engineer, Data Engineer, UI/UX Designer</t>
-  </si>
-  <si>
-    <t>End-to-end AI + data integration pipeline</t>
-  </si>
-  <si>
-    <t>Month 3: Testing &amp; Deployment</t>
-  </si>
-  <si>
-    <t>End-to-end testing, human-in-the-loop workflow, UI refinement, performance tuning, monitoring setup, CI/CD, deployment</t>
-  </si>
-  <si>
-    <t>QA Engineer, MLOps Engineer, Backend Engineer, Integration Engineer, Product Owner, Security Engineer</t>
-  </si>
-  <si>
-    <t>Production-ready MVP with UI and decision workflow</t>
+    <t>Responsibilities in MVP-3</t>
+  </si>
+  <si>
+    <t>Define platform architecture, agent framework, tool registry design, governance strategy</t>
+  </si>
+  <si>
+    <t>Agent orchestration, prompt engineering, multi-step reasoning workflows, evaluation pipelines</t>
+  </si>
+  <si>
+    <t>Decision logic design, scoring models, feedback loop design, performance evaluation</t>
+  </si>
+  <si>
+    <t>RAG pipelines, data ingestion, vector DB setup, data integration workflows</t>
+  </si>
+  <si>
+    <t>FastAPI platform APIs, orchestration layer, configuration-driven execution framework</t>
+  </si>
+  <si>
+    <t>Tool connectors (MCP-style), external API integrations, secure service communication</t>
+  </si>
+  <si>
+    <t>Azure setup, deployment pipelines, model abstraction layer, scalability &amp; infra design</t>
+  </si>
+  <si>
+    <t>80–100%</t>
+  </si>
+  <si>
+    <t>CI/CD for models &amp; pipelines, monitoring, versioning, evaluation automation</t>
+  </si>
+  <si>
+    <t>60–80%</t>
+  </si>
+  <si>
+    <t>Platform testing, workflow validation, tool integration testing, regression testing</t>
+  </si>
+  <si>
+    <t>Define reusable use-case configs, workflows, acceptance criteria</t>
+  </si>
+  <si>
+    <t>40–60%</t>
+  </si>
+  <si>
+    <t>Platform roadmap, prioritization, stakeholder alignment, delivery tracking</t>
+  </si>
+  <si>
+    <t>Platform security, IAM, data protection, AI safety &amp; compliance enforcement</t>
+  </si>
+  <si>
+    <t>UI/UX Designer</t>
+  </si>
+  <si>
+    <t>Platform UI (dashboard), configuration interfaces, usability design</t>
+  </si>
+  <si>
+    <t>20–40%</t>
+  </si>
+  <si>
+    <t>Team Roles</t>
+  </si>
+  <si>
+    <t>Month 1: Platform Foundation</t>
+  </si>
+  <si>
+    <t>- Architecture design &amp; standards- Azure infra setup- Agent core (basic orchestration)- Tool Registry framework- RAG setup (ingestion + vector DB)- LLM abstraction layer</t>
+  </si>
+  <si>
+    <t>AI/ML Architect, Backend Engineer, AI Platform Engineer, Data Engineer, ML Engineer</t>
+  </si>
+  <si>
+    <t>Core platform ready (Agent + Tools + RAG + LLM abstraction)</t>
+  </si>
+  <si>
+    <t>Month 2: Core Development &amp; Integration</t>
+  </si>
+  <si>
+    <t>- Config-driven execution (use-case configs)- Tool connectors (internal + external APIs)- Multi-step agent workflows- RAG integration with decisioning- Basic UI/dashboard- Logging &amp; monitoring setup</t>
+  </si>
+  <si>
+    <t>ML Engineer, Backend Engineer, Integration Engineer, Data Engineer, UI/UX Designer, MLOps Engineer</t>
+  </si>
+  <si>
+    <t>Functional reusable platform with integrated components</t>
+  </si>
+  <si>
+    <t>Month 3: Hardening &amp; Deployment</t>
+  </si>
+  <si>
+    <t>- Security &amp; governance (IAM, RBAC, policies)- AI safety (input/output filtering, PII protection)- Audit logging &amp; observability- Performance tuning &amp; scaling- End-to-end testing- Deployment &amp; first use case onboarding</t>
+  </si>
+  <si>
+    <t>Security Engineer, QA Engineer, MLOps Engineer, Backend Engineer, Product Owner</t>
+  </si>
+  <si>
+    <t>Production-ready platform with governance and first use case live</t>
   </si>
 </sst>
 </file>
@@ -306,7 +303,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{89023D80-EC4C-4E8F-BA26-3750CDA4ED6C}" name="Table1" displayName="Table1" ref="L42:N55" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D14080B6-4727-4D35-BD81-DDEFF9EEFC72}" name="RFP Role"/>
-    <tableColumn id="2" xr3:uid="{349908A4-EFE1-4F1B-BE58-2B4317F383DE}" name="Responsibility in MVP2"/>
+    <tableColumn id="2" xr3:uid="{349908A4-EFE1-4F1B-BE58-2B4317F383DE}" name="Responsibilities in MVP-3"/>
     <tableColumn id="3" xr3:uid="{591E17AC-964B-402E-B2BE-90EFD7A19D72}" name="Allocation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -331,7 +328,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{383A7F68-723D-4D6B-B681-834832A6B569}" name="Phase"/>
     <tableColumn id="2" xr3:uid="{953A1284-F656-4699-BEB5-CED10A77D631}" name="Key Activities"/>
-    <tableColumn id="3" xr3:uid="{4BCC30B5-A8D6-4378-8155-67AC06CC9BAD}" name="Primary Roles"/>
+    <tableColumn id="3" xr3:uid="{4BCC30B5-A8D6-4378-8155-67AC06CC9BAD}" name="Team Roles"/>
     <tableColumn id="4" xr3:uid="{F4B9DDE3-5EA7-4983-AFD6-B211F4B5EDF6}" name="Output"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -656,38 +653,38 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="18" spans="5:14" ht="30" x14ac:dyDescent="0.25">
       <c r="E18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="2">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2">
         <v>8</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>6</v>
       </c>
-      <c r="H18" s="2">
-        <v>4</v>
-      </c>
       <c r="I18" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="5:14" ht="30" x14ac:dyDescent="0.25">
       <c r="E19" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" s="2">
         <v>20</v>
@@ -704,19 +701,19 @@
     </row>
     <row r="20" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E20" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H20" s="2">
         <v>10</v>
       </c>
       <c r="I20" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="5:14" x14ac:dyDescent="0.25">
@@ -755,10 +752,10 @@
     </row>
     <row r="23" spans="5:14" ht="30" x14ac:dyDescent="0.25">
       <c r="E23" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G23" s="2">
         <v>15</v>
@@ -767,24 +764,24 @@
         <v>15</v>
       </c>
       <c r="I23" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="5:14" ht="30" x14ac:dyDescent="0.25">
       <c r="E24" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G24" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I24" s="2">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="5:14" x14ac:dyDescent="0.25">
@@ -806,19 +803,19 @@
     </row>
     <row r="26" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E26" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G26" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I26" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="5:14" x14ac:dyDescent="0.25">
@@ -846,18 +843,18 @@
         <v>10</v>
       </c>
       <c r="G28" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2">
         <v>5</v>
       </c>
       <c r="I28" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="5:14" x14ac:dyDescent="0.25">
       <c r="E29" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" s="2">
         <v>5</v>
@@ -876,16 +873,16 @@
       <c r="E30" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>10</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="2">
         <v>5</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="2">
         <v>5</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="2">
         <v>20</v>
       </c>
       <c r="L30" s="5"/>
@@ -934,10 +931,10 @@
     </row>
     <row r="42" spans="12:14" x14ac:dyDescent="0.25">
       <c r="L42" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>6</v>
@@ -945,10 +942,10 @@
     </row>
     <row r="43" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L43" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>7</v>
@@ -956,10 +953,10 @@
     </row>
     <row r="44" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L44" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N44" s="3">
         <v>1</v>
@@ -967,13 +964,13 @@
     </row>
     <row r="45" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L45" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="12:14" ht="30" x14ac:dyDescent="0.25">
@@ -981,7 +978,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N46" s="3">
         <v>1</v>
@@ -989,10 +986,10 @@
     </row>
     <row r="47" spans="12:14" ht="45" x14ac:dyDescent="0.25">
       <c r="L47" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -1000,46 +997,46 @@
     </row>
     <row r="48" spans="12:14" ht="30" x14ac:dyDescent="0.25">
       <c r="L48" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L49" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="12:19" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L50" s="4" t="s">
         <v>3</v>
       </c>
       <c r="M50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="N50" s="3">
-        <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L51" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N51" s="3">
-        <v>0.5</v>
+      <c r="N51" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="12:19" ht="30" x14ac:dyDescent="0.25">
@@ -1050,29 +1047,29 @@
         <v>40</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L53" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N53" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N53" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="12:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="12:19" ht="30" x14ac:dyDescent="0.25">
       <c r="L54" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="12:19" ht="30" x14ac:dyDescent="0.25">
@@ -1080,66 +1077,66 @@
         <v>44</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="12:19" x14ac:dyDescent="0.25">
       <c r="P56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S56" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="57" spans="12:19" ht="60" x14ac:dyDescent="0.25">
       <c r="P57" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" spans="12:19" ht="60" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="12:19" ht="75" x14ac:dyDescent="0.25">
       <c r="P58" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="12:19" ht="45" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="12:19" ht="90" x14ac:dyDescent="0.25">
       <c r="P59" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
